--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260618.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>4,075,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
